--- a/nriss-update-ip/ig/StructureDefinition-fr-core-documentation-of.xlsx
+++ b/nriss-update-ip/ig/StructureDefinition-fr-core-documentation-of.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T07:58:48+00:00</t>
+    <t>2025-05-23T08:09:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
